--- a/data/gravel/Wilde Rambler SL 2025.xlsx
+++ b/data/gravel/Wilde Rambler SL 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885A50E4-66EE-9440-B2DE-77D04D0DA745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14A22A0-AFD3-C04F-813E-EF73DA488CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34720" yWindow="-17740" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>https://www.wildebikes.com/cdn/shop/files/03062025wilderamblersl2purp-8_2000x.jpg?v=1747333069</t>
   </si>
 </sst>
 </file>
@@ -755,6 +758,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -1224,7 +1232,7 @@
         <v>162.56</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" ref="E31:H31" si="0">AVERAGE(E33,D34)</f>
+        <f t="shared" ref="E31:G31" si="0">AVERAGE(E33,D34)</f>
         <v>170.18</v>
       </c>
       <c r="F31" s="3">
@@ -1250,7 +1258,7 @@
         <v>162.56</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" ref="D32:H32" si="1">E31</f>
+        <f t="shared" ref="D32:F32" si="1">E31</f>
         <v>170.18</v>
       </c>
       <c r="E32" s="3">
@@ -1277,7 +1285,7 @@
         <v>152.4</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:H34" si="2">D35*2.54</f>
+        <f t="shared" ref="D33:G34" si="2">D35*2.54</f>
         <v>162.56</v>
       </c>
       <c r="E33">

--- a/data/gravel/Wilde Rambler SL 2025.xlsx
+++ b/data/gravel/Wilde Rambler SL 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14A22A0-AFD3-C04F-813E-EF73DA488CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6EC4B-4FA8-C248-8E1D-5CCD08169C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10660" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -236,148 +236,145 @@
     <t>base_build</t>
   </si>
   <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
+  </si>
+  <si>
+    <t>threaded</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>X-Small</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>X-Large</t>
+  </si>
+  <si>
+    <t>Recommended Rider Height</t>
+  </si>
+  <si>
+    <t>Head Tube Angle (°)</t>
+  </si>
+  <si>
+    <t>Seat Tube Angle (°)</t>
+  </si>
+  <si>
+    <t>Seat Tube Length ctc (mm)</t>
+  </si>
+  <si>
+    <t>Stack (mm)</t>
+  </si>
+  <si>
+    <t>Reach (mm)</t>
+  </si>
+  <si>
+    <t>Chainstay Length (mm)</t>
+  </si>
+  <si>
+    <t>Fork ATC (mm)</t>
+  </si>
+  <si>
+    <t>Rake (mm)</t>
+  </si>
+  <si>
+    <t>Trail (mm)</t>
+  </si>
+  <si>
+    <t>Headtube Extension (mm)</t>
+  </si>
+  <si>
+    <t>BB Drop (mm)</t>
+  </si>
+  <si>
+    <t>Rambler SL Gravel</t>
+  </si>
+  <si>
+    <t>https://www.wildebikes.com/collections/bikes/products/rambler-sl</t>
+  </si>
+  <si>
+    <t>steel</t>
+  </si>
+  <si>
+    <t>5' to 5'4"</t>
+  </si>
+  <si>
+    <t>5'4" to 5'7"</t>
+  </si>
+  <si>
+    <t>5'7" to 5'9"</t>
+  </si>
+  <si>
+    <t>5'9" to 6'</t>
+  </si>
+  <si>
+    <t>6' to 6'3"</t>
+  </si>
+  <si>
+    <t>Headtube Length (mm)</t>
+  </si>
+  <si>
+    <t>Top Tube Length Effective (mm)</t>
+  </si>
+  <si>
+    <t>Standover (mm)</t>
+  </si>
+  <si>
+    <t>https://www.wildebikes.com/cdn/shop/files/03062025wilderamblersl2purp-8_2000x.jpg?v=1747333069</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>a8:g32</t>
+  </si>
+  <si>
     <t>custom_builds</t>
-  </si>
-  <si>
-    <t>currency</t>
-  </si>
-  <si>
-    <t>class</t>
-  </si>
-  <si>
-    <t>gravel</t>
-  </si>
-  <si>
-    <t>handlebar</t>
-  </si>
-  <si>
-    <t>drop bar</t>
-  </si>
-  <si>
-    <t>fork</t>
-  </si>
-  <si>
-    <t>rigid</t>
-  </si>
-  <si>
-    <t>threaded</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>external</t>
-  </si>
-  <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>X-Small</t>
-  </si>
-  <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>X-Large</t>
-  </si>
-  <si>
-    <t>Recommended Rider Height</t>
-  </si>
-  <si>
-    <t>Head Tube Angle (°)</t>
-  </si>
-  <si>
-    <t>Seat Tube Angle (°)</t>
-  </si>
-  <si>
-    <t>Seat Tube Length ctc (mm)</t>
-  </si>
-  <si>
-    <t>Stack (mm)</t>
-  </si>
-  <si>
-    <t>Reach (mm)</t>
-  </si>
-  <si>
-    <t>Chainstay Length (mm)</t>
-  </si>
-  <si>
-    <t>Fork ATC (mm)</t>
-  </si>
-  <si>
-    <t>Rake (mm)</t>
-  </si>
-  <si>
-    <t>Trail (mm)</t>
-  </si>
-  <si>
-    <t>Headtube Extension (mm)</t>
-  </si>
-  <si>
-    <t>BB Drop (mm)</t>
-  </si>
-  <si>
-    <t>usd</t>
-  </si>
-  <si>
-    <t>Rambler SL Gravel</t>
-  </si>
-  <si>
-    <t>https://www.wildebikes.com/collections/bikes/products/rambler-sl</t>
-  </si>
-  <si>
-    <t>steel</t>
-  </si>
-  <si>
-    <t>5' to 5'4"</t>
-  </si>
-  <si>
-    <t>5'4" to 5'7"</t>
-  </si>
-  <si>
-    <t>5'7" to 5'9"</t>
-  </si>
-  <si>
-    <t>5'9" to 6'</t>
-  </si>
-  <si>
-    <t>6' to 6'3"</t>
-  </si>
-  <si>
-    <t>Headtube Length (mm)</t>
-  </si>
-  <si>
-    <t>Top Tube Length Effective (mm)</t>
-  </si>
-  <si>
-    <t>Standover (mm)</t>
-  </si>
-  <si>
-    <t>a8:g34</t>
-  </si>
-  <si>
-    <t>https://www.wildebikes.com/cdn/shop/files/03062025wilderamblersl2purp-8_2000x.jpg?v=1747333069</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
@@ -411,11 +408,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -731,7 +727,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -755,12 +751,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -776,22 +772,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="F8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -799,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>70.5</v>
@@ -822,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>74</v>
@@ -845,7 +841,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11">
         <v>105</v>
@@ -868,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C12">
         <v>425</v>
@@ -891,7 +887,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>524</v>
@@ -914,7 +910,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <v>533</v>
@@ -937,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C15">
         <v>370</v>
@@ -960,7 +956,7 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C16">
         <v>67</v>
@@ -978,12 +974,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C17">
         <v>425</v>
@@ -1001,12 +997,12 @@
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>398</v>
@@ -1024,12 +1020,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C19">
         <v>49</v>
@@ -1047,12 +1043,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C20">
         <v>69</v>
@@ -1070,12 +1066,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C21">
         <v>741</v>
@@ -1093,12 +1089,12 @@
         <v>831</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C22">
         <v>45</v>
@@ -1116,17 +1112,17 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1134,7 +1130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1142,12 +1138,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1170,7 +1166,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1193,7 +1189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1216,435 +1212,383 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="3">
-        <f>C33</f>
+      <c r="C31">
+        <f>C33*2.54</f>
         <v>152.4</v>
       </c>
-      <c r="D31" s="3">
-        <f>AVERAGE(D33,C34)</f>
+      <c r="D31">
+        <f t="shared" ref="D31:G32" si="0">D33*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="E31" s="3">
-        <f t="shared" ref="E31:G31" si="0">AVERAGE(E33,D34)</f>
+      <c r="E31">
+        <f t="shared" si="0"/>
         <v>170.18</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31">
         <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="3">
-        <f>D31</f>
+      <c r="C32">
+        <f>C34*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D32" s="3">
-        <f t="shared" ref="D32:F32" si="1">E31</f>
+      <c r="D32">
+        <f t="shared" si="0"/>
         <v>170.18</v>
       </c>
-      <c r="E32" s="3">
-        <f t="shared" si="1"/>
+      <c r="E32">
+        <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
-      <c r="F32" s="3">
-        <f t="shared" si="1"/>
+      <c r="F32">
+        <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
-      <c r="G32" s="3">
-        <f>G36</f>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>190.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>60</v>
+      </c>
+      <c r="D33">
+        <v>64</v>
+      </c>
+      <c r="E33">
+        <v>67</v>
+      </c>
+      <c r="F33">
+        <v>69</v>
+      </c>
+      <c r="G33">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>64</v>
+      </c>
+      <c r="D34">
+        <v>67</v>
+      </c>
+      <c r="E34">
+        <v>69</v>
+      </c>
+      <c r="F34">
+        <v>72</v>
+      </c>
+      <c r="G34">
         <v>75</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33">
-        <f>C35*2.54</f>
-        <v>152.4</v>
-      </c>
-      <c r="D33">
-        <f t="shared" ref="D33:G34" si="2">D35*2.54</f>
-        <v>162.56</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="2"/>
-        <v>175.26</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="2"/>
-        <v>182.88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34">
-        <f>C36*2.54</f>
-        <v>162.56</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="2"/>
-        <v>175.26</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="2"/>
-        <v>182.88</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="2"/>
-        <v>190.5</v>
-      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C35">
-        <v>60</v>
-      </c>
-      <c r="D35">
-        <v>64</v>
-      </c>
-      <c r="E35">
-        <v>67</v>
-      </c>
-      <c r="F35">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
         <v>69</v>
       </c>
-      <c r="G35">
-        <v>72</v>
+      <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36">
-        <v>64</v>
-      </c>
-      <c r="D36">
-        <v>67</v>
-      </c>
-      <c r="E36">
-        <v>69</v>
-      </c>
-      <c r="F36">
-        <v>72</v>
-      </c>
-      <c r="G36">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" t="s">
-        <v>104</v>
-      </c>
-      <c r="F37" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" t="s">
-        <v>106</v>
-      </c>
-      <c r="I37" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>76</v>
+        <v>37</v>
+      </c>
+      <c r="B41">
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44">
-        <v>2.2999999999999998</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="B47">
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49">
-        <v>142</v>
+        <v>45</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50">
-        <v>100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
+      </c>
+      <c r="B51">
+        <v>27.2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="B69">
+        <v>1600</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71">
-        <v>1600</v>
+        <v>111</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilde Rambler SL 2025.xlsx
+++ b/data/gravel/Wilde Rambler SL 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6EC4B-4FA8-C248-8E1D-5CCD08169C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF67D88-303A-9D4A-BD95-02D5821386A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10660" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,24 @@
   </si>
   <si>
     <t>custom_builds</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -708,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1419,120 +1437,105 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>75</v>
@@ -1540,36 +1543,36 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B69">
-        <v>1600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>75</v>
@@ -1577,17 +1580,62 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>111</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>109</v>
       </c>
     </row>
